--- a/ContractRates_V1.xlsx
+++ b/ContractRates_V1.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C14322-A7A3-4474-AF78-3A82401D9181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0465B1BD-D9FD-4CB1-997C-F69C5F9F29CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="API Meta Data" sheetId="1" r:id="rId1"/>
@@ -482,9 +482,6 @@
     <t>Single</t>
   </si>
   <si>
-    <t>Contract Rates API</t>
-  </si>
-  <si>
     <t>API for getting Contract Rates</t>
   </si>
   <si>
@@ -549,6 +546,9 @@
   </si>
   <si>
     <t>HTTP-Basic</t>
+  </si>
+  <si>
+    <t>Contract Rates API Test</t>
   </si>
 </sst>
 </file>
@@ -1137,40 +1137,22 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1179,10 +1161,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1221,25 +1209,37 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1252,18 +1252,6 @@
     <cellStyle name="Normal_Data Dictionary" xfId="3" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="79">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1612,6 +1600,18 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1950,36 +1950,36 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{42CFF3B7-0F5A-4607-A3E4-9358F518D2D9}" name="Table2891011131415161022" displayName="Table2891011131415161022" ref="A67:B68" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{42CFF3B7-0F5A-4607-A3E4-9358F518D2D9}" name="Table2891011131415161022" displayName="Table2891011131415161022" ref="A67:B68" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A67:B68" xr:uid="{42CFF3B7-0F5A-4607-A3E4-9358F518D2D9}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D38CDA0E-520B-49CA-B562-AA29782EE256}" name=" Field" dataDxfId="1" dataCellStyle="Normal_Data Dictionary"/>
-    <tableColumn id="2" xr3:uid="{F431979B-86CC-45DB-9851-C4F9203529FB}" name="Data Type" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D38CDA0E-520B-49CA-B562-AA29782EE256}" name=" Field" dataDxfId="16" dataCellStyle="Normal_Data Dictionary"/>
+    <tableColumn id="2" xr3:uid="{F431979B-86CC-45DB-9851-C4F9203529FB}" name="Data Type" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="55" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="StringDefinitionTable" displayName="StringDefinitionTable" ref="A5:I10" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14" headerRowCellStyle="Normal 24 2 2 5 2" dataCellStyle="Normal 10 13 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="55" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="StringDefinitionTable" displayName="StringDefinitionTable" ref="A5:I10" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10" headerRowCellStyle="Normal 24 2 2 5 2" dataCellStyle="Normal 10 13 2 2">
   <autoFilter ref="A5:I10" xr:uid="{00000000-0009-0000-0100-000037000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="String Name" dataDxfId="13" dataCellStyle="Normal 10 13 2 2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="Description" dataDxfId="12" dataCellStyle="Normal 10 13 2 2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="String Format" dataDxfId="11" dataCellStyle="Normal 10 13 2 2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="Minimum Length" dataDxfId="10" dataCellStyle="Normal 10 13 2 2"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="Maximum Length" dataDxfId="9" dataCellStyle="Normal 10 13 2 2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Required" dataDxfId="8" dataCellStyle="Normal 10 13 2 2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Default Value" dataDxfId="7" dataCellStyle="Normal 10 13 2 2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="Example Value" dataDxfId="6" dataCellStyle="Normal 10 13 2 2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0A00-000006000000}" name="Pattern" dataDxfId="5" dataCellStyle="Normal 10 13 2 2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="String Name" dataDxfId="9" dataCellStyle="Normal 10 13 2 2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="Description" dataDxfId="8" dataCellStyle="Normal 10 13 2 2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="String Format" dataDxfId="7" dataCellStyle="Normal 10 13 2 2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="Minimum Length" dataDxfId="6" dataCellStyle="Normal 10 13 2 2"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="Maximum Length" dataDxfId="5" dataCellStyle="Normal 10 13 2 2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Required" dataDxfId="4" dataCellStyle="Normal 10 13 2 2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Default Value" dataDxfId="3" dataCellStyle="Normal 10 13 2 2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="Example Value" dataDxfId="2" dataCellStyle="Normal 10 13 2 2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0A00-000006000000}" name="Pattern" dataDxfId="1" dataCellStyle="Normal 10 13 2 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="56" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="NumberDefinitionTable" displayName="NumberDefinitionTable" ref="A14:G19" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="56" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="NumberDefinitionTable" displayName="NumberDefinitionTable" ref="A14:G19" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A14:G19" xr:uid="{00000000-0009-0000-0100-000038000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="Name"/>
@@ -2359,9 +2359,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="27.453125" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="21">
@@ -2392,7 +2392,7 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
     </row>
-    <row r="3" spans="1:24" ht="17" hidden="1">
+    <row r="3" spans="1:24" ht="17.25" hidden="1">
       <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
@@ -2403,7 +2403,7 @@
       </c>
     </row>
     <row r="4" spans="1:24" hidden="1"/>
-    <row r="5" spans="1:24" ht="18.5">
+    <row r="5" spans="1:24" ht="18.75">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -2432,7 +2432,7 @@
       <c r="X5" s="5"/>
     </row>
     <row r="6" spans="1:24" hidden="1"/>
-    <row r="7" spans="1:24" ht="17" hidden="1">
+    <row r="7" spans="1:24" ht="17.25" hidden="1">
       <c r="A7" s="26" t="s">
         <v>4</v>
       </c>
@@ -2442,27 +2442,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="17">
+    <row r="9" spans="1:24" ht="17.25">
       <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="26"/>
       <c r="C9" s="26"/>
       <c r="D9" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" ht="17">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="17.25">
       <c r="A11" s="26" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="26"/>
       <c r="C11" s="26"/>
       <c r="D11" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="18.5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="18.75">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -2490,7 +2490,7 @@
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
     </row>
-    <row r="15" spans="1:24" ht="17">
+    <row r="15" spans="1:24" ht="17.25">
       <c r="A15" s="26" t="s">
         <v>9</v>
       </c>
@@ -2498,7 +2498,7 @@
       <c r="C15" s="26"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="17" spans="1:24" ht="18.5">
+    <row r="17" spans="1:24" ht="18.75">
       <c r="A17" s="5" t="s">
         <v>10</v>
       </c>
@@ -2526,14 +2526,14 @@
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
     </row>
-    <row r="19" spans="1:24" ht="17">
+    <row r="19" spans="1:24" ht="17.25">
       <c r="A19" s="26" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="27"/>
       <c r="D19" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2558,17 +2558,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M48"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="18.26953125" customWidth="1"/>
+    <col min="1" max="3" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" customWidth="1"/>
-    <col min="6" max="6" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.1796875" customWidth="1"/>
-    <col min="8" max="8" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.453125" customWidth="1"/>
-    <col min="10" max="10" width="18.1796875" customWidth="1"/>
-    <col min="11" max="11" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21">
@@ -2597,7 +2597,7 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:13" ht="18.5" hidden="1">
+    <row r="3" spans="1:13" ht="18.75" hidden="1">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -2638,7 +2638,7 @@
     <row r="8" spans="1:13" hidden="1"/>
     <row r="9" spans="1:13" hidden="1"/>
     <row r="10" spans="1:13" hidden="1"/>
-    <row r="11" spans="1:13" ht="18.5">
+    <row r="11" spans="1:13" ht="18.75">
       <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
@@ -2680,19 +2680,19 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>154</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>155</v>
       </c>
       <c r="C14" t="s">
         <v>77</v>
       </c>
       <c r="D14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14" t="s">
         <v>156</v>
-      </c>
-      <c r="F14" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -2711,7 +2711,7 @@
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
     </row>
-    <row r="20" spans="1:13" ht="18.5">
+    <row r="20" spans="1:13" ht="18.75">
       <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
@@ -2753,13 +2753,13 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s">
         <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D23" t="s">
         <v>119</v>
@@ -2820,7 +2820,7 @@
       <c r="A40" s="7"/>
       <c r="G40" s="8"/>
     </row>
-    <row r="41" spans="1:13" ht="18.5">
+    <row r="41" spans="1:13" ht="18.75">
       <c r="A41" s="9" t="s">
         <v>31</v>
       </c>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B44" s="14">
         <v>200</v>
@@ -2880,7 +2880,7 @@
         <v>89</v>
       </c>
       <c r="G44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2945,7 +2945,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M234"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="36" bestFit="1" customWidth="1"/>
   </cols>
@@ -2972,7 +2972,7 @@
         <v>33</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3009,7 +3009,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>54</v>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>54</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>54</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>89</v>
@@ -3248,7 +3248,7 @@
         <v>33</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3293,7 +3293,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B52" s="24" t="s">
         <v>54</v>
@@ -3301,7 +3301,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B53" s="24" t="s">
         <v>89</v>
@@ -3320,7 +3320,7 @@
         <v>33</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3344,7 +3344,7 @@
         <v>109</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3352,7 +3352,7 @@
         <v>33</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3365,7 +3365,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B63" s="24" t="s">
         <v>89</v>
@@ -3384,7 +3384,7 @@
         <v>33</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3397,7 +3397,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B68" s="24" t="s">
         <v>89</v>
@@ -3412,7 +3412,7 @@
         <v>33</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3433,7 +3433,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B74" s="24" t="s">
         <v>89</v>
@@ -3708,7 +3708,7 @@
         <v>33</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3769,7 +3769,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B121" s="24" t="s">
         <v>89</v>
@@ -3780,7 +3780,7 @@
         <v>33</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3865,7 +3865,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B134" s="24" t="s">
         <v>148</v>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B135" s="24" t="s">
         <v>148</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B136" s="24" t="s">
         <v>148</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B137" s="24" t="s">
         <v>148</v>
@@ -3933,16 +3933,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.453125" customWidth="1"/>
-    <col min="2" max="2" width="18.26953125" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" customWidth="1"/>
-    <col min="5" max="6" width="18.453125" customWidth="1"/>
-    <col min="7" max="7" width="18.1796875" customWidth="1"/>
-    <col min="8" max="11" width="18.453125" customWidth="1"/>
-    <col min="12" max="13" width="18.26953125" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="6" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22.5" customHeight="1">
@@ -3963,7 +3963,7 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="30" customHeight="1"/>
-    <row r="3" spans="1:13" ht="18.5">
+    <row r="3" spans="1:13" ht="18.75">
       <c r="A3" s="5" t="s">
         <v>54</v>
       </c>
@@ -4071,7 +4071,7 @@
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
     </row>
-    <row r="12" spans="1:13" ht="18.5">
+    <row r="12" spans="1:13" ht="18.75">
       <c r="A12" s="5" t="s">
         <v>59</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="18.5">
+    <row r="21" spans="1:9" ht="18.75">
       <c r="A21" s="5" t="s">
         <v>71</v>
       </c>
@@ -4165,7 +4165,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20" ht="21">
       <c r="A1" s="1" t="s">
@@ -4191,7 +4191,7 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="18.5">
+    <row r="3" spans="1:20" ht="18.75">
       <c r="A3" s="5" t="s">
         <v>37</v>
       </c>
@@ -4207,83 +4207,83 @@
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:20" ht="15" thickBot="1"/>
-    <row r="5" spans="1:20" ht="21.5" thickBot="1">
-      <c r="D5" s="29" t="s">
+    <row r="4" spans="1:20" ht="15.75" thickBot="1"/>
+    <row r="5" spans="1:20" ht="21.75" thickBot="1">
+      <c r="D5" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="32" t="s">
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="33"/>
-    </row>
-    <row r="6" spans="1:20" ht="15" thickTop="1">
-      <c r="D6" s="34" t="s">
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="57"/>
+    </row>
+    <row r="6" spans="1:20" ht="15.75" thickTop="1">
+      <c r="D6" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="37" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="39"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="63"/>
     </row>
     <row r="7" spans="1:20">
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="43" t="s">
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="45"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="41"/>
     </row>
     <row r="8" spans="1:20">
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="43" t="s">
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" thickBot="1">
-      <c r="D9" s="46" t="s">
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="41"/>
+    </row>
+    <row r="9" spans="1:20" ht="15.75" thickBot="1">
+      <c r="D9" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49" t="s">
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="51"/>
-    </row>
-    <row r="11" spans="1:20" ht="18.5">
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="47"/>
+    </row>
+    <row r="11" spans="1:20" ht="18.75">
       <c r="A11" s="5" t="s">
         <v>44</v>
       </c>
@@ -4300,89 +4300,89 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" spans="1:20" ht="15" thickBot="1"/>
-    <row r="13" spans="1:20" ht="22" thickTop="1" thickBot="1">
-      <c r="D13" s="52" t="s">
+    <row r="12" spans="1:20" ht="15.75" thickBot="1"/>
+    <row r="13" spans="1:20" ht="22.5" thickTop="1" thickBot="1">
+      <c r="D13" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="52" t="s">
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="56"/>
-    </row>
-    <row r="14" spans="1:20" ht="15" thickTop="1">
-      <c r="D14" s="62" t="s">
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="52"/>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" thickTop="1">
+      <c r="D14" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="44" t="s">
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="63"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="38"/>
     </row>
     <row r="15" spans="1:20">
-      <c r="D15" s="62" t="s">
+      <c r="D15" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="44" t="s">
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="63"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="38"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="D16" s="62" t="s">
+      <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="44" t="s">
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="63"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" thickBot="1">
-      <c r="D17" s="57" t="s">
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="38"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" thickBot="1">
+      <c r="D17" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="60" t="s">
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="60"/>
-      <c r="M17" s="61"/>
-    </row>
-    <row r="18" spans="1:13" ht="15" thickTop="1"/>
-    <row r="19" spans="1:13" ht="18.5">
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="33"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickTop="1"/>
+    <row r="19" spans="1:13" ht="18.75">
       <c r="A19" s="5" t="s">
         <v>35</v>
       </c>
@@ -4401,6 +4401,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:L9"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="H13:M13"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="H17:M17"/>
     <mergeCell ref="D14:G14"/>
@@ -4409,18 +4421,6 @@
     <mergeCell ref="H15:M15"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="H16:M16"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="H8:L8"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="H9:L9"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="H7:L7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/ContractRates_V1.xlsx
+++ b/ContractRates_V1.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="183">
   <si>
     <t>API Entry Sheet</t>
   </si>
@@ -549,12 +549,37 @@
   </si>
   <si>
     <t>Contract Rates API Test</t>
+  </si>
+  <si>
+    <t>openAPIVersionName</t>
+  </si>
+  <si>
+    <t>apiVersionName</t>
+  </si>
+  <si>
+    <t>apiTitleName</t>
+  </si>
+  <si>
+    <t>apiDescriptionName</t>
+  </si>
+  <si>
+    <t>serverURLName</t>
+  </si>
+  <si>
+    <t>apiAuthenticationName</t>
+  </si>
+  <si>
+    <t>TestSuresh</t>
+  </si>
+  <si>
+    <t>Test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="14">
     <font>
       <sz val="11"/>
@@ -2361,7 +2386,7 @@
   <dimension ref="A1:X19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="4" max="4" customWidth="true" width="27.42578125" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="21">
@@ -2396,7 +2421,9 @@
       <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="26"/>
+      <c r="B3" s="26" t="s">
+        <v>175</v>
+      </c>
       <c r="C3" s="27"/>
       <c r="D3" s="4" t="s">
         <v>2</v>
@@ -2436,7 +2463,9 @@
       <c r="A7" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="26"/>
+      <c r="B7" s="26" t="s">
+        <v>176</v>
+      </c>
       <c r="C7" s="26"/>
       <c r="D7" s="4" t="s">
         <v>5</v>
@@ -2446,7 +2475,9 @@
       <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="26"/>
+      <c r="B9" s="26" t="s">
+        <v>177</v>
+      </c>
       <c r="C9" s="26"/>
       <c r="D9" s="4" t="s">
         <v>174</v>
@@ -2456,7 +2487,9 @@
       <c r="A11" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="26"/>
+      <c r="B11" s="26" t="s">
+        <v>178</v>
+      </c>
       <c r="C11" s="26"/>
       <c r="D11" s="4" t="s">
         <v>152</v>
@@ -2494,13 +2527,15 @@
       <c r="A15" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="26"/>
+      <c r="B15" s="26" t="s">
+        <v>179</v>
+      </c>
       <c r="C15" s="26"/>
       <c r="D15" s="4"/>
     </row>
     <row r="17" spans="1:24" ht="18.75">
       <c r="A17" s="5" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -2528,7 +2563,7 @@
     </row>
     <row r="19" spans="1:24" ht="17.25">
       <c r="A19" s="26" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="27"/>
@@ -2560,15 +2595,15 @@
   <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="1" max="3" customWidth="true" width="18.28515625" collapsed="false"/>
+    <col min="4" max="4" customWidth="true" width="18.0" collapsed="false"/>
+    <col min="5" max="5" customWidth="true" width="18.140625" collapsed="false"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="24.5703125" collapsed="false"/>
+    <col min="7" max="7" customWidth="true" width="18.140625" collapsed="false"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="22.7109375" collapsed="false"/>
+    <col min="9" max="9" customWidth="true" width="18.42578125" collapsed="false"/>
+    <col min="10" max="10" customWidth="true" width="18.140625" collapsed="false"/>
+    <col min="11" max="11" customWidth="true" width="18.28515625" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21">
@@ -2680,36 +2715,52 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="F14" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="20" spans="1:13" ht="18.75">
       <c r="A20" s="5" t="s">
@@ -2753,59 +2804,85 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="7"/>
+      <c r="A24" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="7"/>
+      <c r="A25" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="7"/>
+      <c r="A26" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="7"/>
+      <c r="A27" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="7"/>
+      <c r="A28" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="7"/>
+      <c r="A29" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="7"/>
+      <c r="A30" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="7"/>
+      <c r="A31" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="7"/>
+      <c r="A32" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="7"/>
+      <c r="A33" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="7"/>
+      <c r="A34" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="7"/>
+      <c r="A35" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="7"/>
+      <c r="A36" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="7"/>
@@ -2862,47 +2939,73 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B44" s="14">
-        <v>200</v>
+        <v>182</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>182</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="F44" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="G44" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
+      <c r="A45" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
+      <c r="A46" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="G47" s="22"/>
+      <c r="A47" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="G47" s="22" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
+      <c r="A48" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="8">
@@ -2947,7 +3050,7 @@
   <dimension ref="A1:M234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" bestFit="true" customWidth="true" width="36.0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21">
@@ -2985,7 +3088,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="12" t="s">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>89</v>
@@ -2993,7 +3096,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="12" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>89</v>
@@ -3001,7 +3104,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="12" t="s">
-        <v>85</v>
+        <v>182</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>89</v>
@@ -3009,7 +3112,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="23" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>54</v>
@@ -3017,7 +3120,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="23" t="s">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>89</v>
@@ -3025,7 +3128,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="23" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>54</v>
@@ -3033,7 +3136,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="23" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>54</v>
@@ -3041,7 +3144,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="23" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>89</v>
@@ -3072,7 +3175,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="12" t="s">
-        <v>90</v>
+        <v>182</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>54</v>
@@ -3080,7 +3183,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="23" t="s">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>54</v>
@@ -3088,7 +3191,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="23" t="s">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>54</v>
@@ -3096,7 +3199,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="23" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>54</v>
@@ -3104,7 +3207,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="23" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>54</v>
@@ -3112,7 +3215,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="23" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>54</v>
@@ -3120,7 +3223,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="23" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>54</v>
@@ -3128,7 +3231,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="24" t="s">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>54</v>
@@ -3152,7 +3255,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="12" t="s">
-        <v>81</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3397,7 +3500,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="12" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="B68" s="24" t="s">
         <v>89</v>
@@ -3425,7 +3528,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="12" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="B73" s="24" t="s">
         <v>89</v>
@@ -3433,7 +3536,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="25" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B74" s="24" t="s">
         <v>89</v>
@@ -3457,7 +3560,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="12" t="s">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="B78" s="24" t="s">
         <v>54</v>
@@ -3465,7 +3568,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="25" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
       <c r="B79" s="24" t="s">
         <v>89</v>
@@ -3473,7 +3576,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="25" t="s">
-        <v>121</v>
+        <v>182</v>
       </c>
       <c r="B80" s="24" t="s">
         <v>89</v>
@@ -3481,7 +3584,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="25" t="s">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="B81" s="24" t="s">
         <v>54</v>
@@ -3489,7 +3592,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="25" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="B82" s="24" t="s">
         <v>54</v>
@@ -3497,7 +3600,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="25" t="s">
-        <v>123</v>
+        <v>182</v>
       </c>
       <c r="B83" s="24" t="s">
         <v>148</v>
@@ -3505,7 +3608,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="25" t="s">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="B84" s="24" t="s">
         <v>148</v>
@@ -3513,7 +3616,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="25" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="B85" s="24" t="s">
         <v>54</v>
@@ -3521,7 +3624,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="B86" s="24" t="s">
         <v>54</v>
@@ -3529,7 +3632,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="25" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="B87" s="24" t="s">
         <v>89</v>
@@ -3553,7 +3656,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="12" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="B91" s="24" t="s">
         <v>54</v>
@@ -3561,7 +3664,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="25" t="s">
-        <v>103</v>
+        <v>182</v>
       </c>
       <c r="B92" s="24" t="s">
         <v>54</v>
@@ -3585,7 +3688,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="12" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="B96" s="24" t="s">
         <v>54</v>
@@ -3593,7 +3696,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="25" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="B97" s="24" t="s">
         <v>54</v>
@@ -3617,7 +3720,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="12" t="s">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="B101" s="24" t="s">
         <v>54</v>
@@ -3625,7 +3728,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="25" t="s">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="B102" s="24" t="s">
         <v>54</v>
@@ -3633,7 +3736,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="25" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="B103" s="24" t="s">
         <v>54</v>
@@ -3641,7 +3744,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="25" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="B104" s="24" t="s">
         <v>54</v>
@@ -3649,7 +3752,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="25" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="B105" s="24" t="s">
         <v>54</v>
@@ -3657,7 +3760,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="25" t="s">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="B106" s="24" t="s">
         <v>54</v>
@@ -3665,7 +3768,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="25" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="B107" s="24" t="s">
         <v>54</v>
@@ -3673,7 +3776,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="25" t="s">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="B108" s="24" t="s">
         <v>54</v>
@@ -3681,7 +3784,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="25" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="B109" s="24" t="s">
         <v>54</v>
@@ -3689,7 +3792,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="25" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="B110" s="24" t="s">
         <v>54</v>
@@ -3697,7 +3800,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="25" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="B111" s="24" t="s">
         <v>54</v>
@@ -3721,7 +3824,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="12" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="B115" s="24" t="s">
         <v>148</v>
@@ -3729,7 +3832,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="25" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="B116" s="24" t="s">
         <v>148</v>
@@ -3737,7 +3840,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="25" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="B117" s="24" t="s">
         <v>148</v>
@@ -3745,7 +3848,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="25" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="B118" s="24" t="s">
         <v>148</v>
@@ -3753,7 +3856,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="25" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="B119" s="24" t="s">
         <v>54</v>
@@ -3761,7 +3864,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="25" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="B120" s="24" t="s">
         <v>54</v>
@@ -3769,7 +3872,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="25" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B121" s="24" t="s">
         <v>89</v>
@@ -3793,7 +3896,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="12" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="B125" s="24" t="s">
         <v>54</v>
@@ -3801,7 +3904,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="25" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="B126" s="24" t="s">
         <v>54</v>
@@ -3809,7 +3912,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="25" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="B127" s="24" t="s">
         <v>148</v>
@@ -3817,7 +3920,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="25" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="B128" s="24" t="s">
         <v>54</v>
@@ -3825,7 +3928,7 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="25" t="s">
-        <v>116</v>
+        <v>182</v>
       </c>
       <c r="B129" s="24" t="s">
         <v>54</v>
@@ -3833,7 +3936,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="25" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="B130" s="24" t="s">
         <v>54</v>
@@ -3841,7 +3944,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="25" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="B131" s="24" t="s">
         <v>89</v>
@@ -3849,7 +3952,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="25" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="B132" s="24" t="s">
         <v>148</v>
@@ -3857,7 +3960,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="25" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="B133" s="24" t="s">
         <v>148</v>
@@ -3865,7 +3968,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="25" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B134" s="24" t="s">
         <v>148</v>
@@ -3873,7 +3976,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="25" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B135" s="24" t="s">
         <v>148</v>
@@ -3881,7 +3984,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="25" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B136" s="24" t="s">
         <v>148</v>
@@ -3889,7 +3992,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="25" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B137" s="24" t="s">
         <v>148</v>
@@ -3935,14 +4038,14 @@
   <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="6" width="18.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
-    <col min="8" max="11" width="18.42578125" customWidth="1"/>
-    <col min="12" max="13" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="18.42578125" collapsed="false"/>
+    <col min="2" max="2" customWidth="true" width="18.28515625" collapsed="false"/>
+    <col min="3" max="3" customWidth="true" width="18.140625" collapsed="false"/>
+    <col min="4" max="4" customWidth="true" width="18.28515625" collapsed="false"/>
+    <col min="5" max="6" customWidth="true" width="18.42578125" collapsed="false"/>
+    <col min="7" max="7" customWidth="true" width="18.140625" collapsed="false"/>
+    <col min="8" max="11" customWidth="true" width="18.42578125" collapsed="false"/>
+    <col min="12" max="13" customWidth="true" width="18.28515625" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22.5" customHeight="1">

--- a/ContractRates_V1.xlsx
+++ b/ContractRates_V1.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="175">
   <si>
     <t>API Entry Sheet</t>
   </si>
@@ -549,37 +549,12 @@
   </si>
   <si>
     <t>Contract Rates API Test</t>
-  </si>
-  <si>
-    <t>openAPIVersionName</t>
-  </si>
-  <si>
-    <t>apiVersionName</t>
-  </si>
-  <si>
-    <t>apiTitleName</t>
-  </si>
-  <si>
-    <t>apiDescriptionName</t>
-  </si>
-  <si>
-    <t>serverURLName</t>
-  </si>
-  <si>
-    <t>apiAuthenticationName</t>
-  </si>
-  <si>
-    <t>TestSuresh</t>
-  </si>
-  <si>
-    <t>Test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="14">
     <font>
       <sz val="11"/>
@@ -2386,7 +2361,7 @@
   <dimension ref="A1:X19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" customWidth="true" width="27.42578125" collapsed="false"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="21">
@@ -2421,9 +2396,7 @@
       <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>175</v>
-      </c>
+      <c r="B3" s="26"/>
       <c r="C3" s="27"/>
       <c r="D3" s="4" t="s">
         <v>2</v>
@@ -2463,9 +2436,7 @@
       <c r="A7" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>176</v>
-      </c>
+      <c r="B7" s="26"/>
       <c r="C7" s="26"/>
       <c r="D7" s="4" t="s">
         <v>5</v>
@@ -2475,9 +2446,7 @@
       <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>177</v>
-      </c>
+      <c r="B9" s="26"/>
       <c r="C9" s="26"/>
       <c r="D9" s="4" t="s">
         <v>174</v>
@@ -2487,9 +2456,7 @@
       <c r="A11" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>178</v>
-      </c>
+      <c r="B11" s="26"/>
       <c r="C11" s="26"/>
       <c r="D11" s="4" t="s">
         <v>152</v>
@@ -2527,15 +2494,13 @@
       <c r="A15" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>179</v>
-      </c>
+      <c r="B15" s="26"/>
       <c r="C15" s="26"/>
       <c r="D15" s="4"/>
     </row>
     <row r="17" spans="1:24" ht="18.75">
       <c r="A17" s="5" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -2563,7 +2528,7 @@
     </row>
     <row r="19" spans="1:24" ht="17.25">
       <c r="A19" s="26" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="27"/>
@@ -2595,15 +2560,15 @@
   <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" customWidth="true" width="18.28515625" collapsed="false"/>
-    <col min="4" max="4" customWidth="true" width="18.0" collapsed="false"/>
-    <col min="5" max="5" customWidth="true" width="18.140625" collapsed="false"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="24.5703125" collapsed="false"/>
-    <col min="7" max="7" customWidth="true" width="18.140625" collapsed="false"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="22.7109375" collapsed="false"/>
-    <col min="9" max="9" customWidth="true" width="18.42578125" collapsed="false"/>
-    <col min="10" max="10" customWidth="true" width="18.140625" collapsed="false"/>
-    <col min="11" max="11" customWidth="true" width="18.28515625" collapsed="false"/>
+    <col min="1" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21">
@@ -2715,52 +2680,36 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="C14" t="s">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="F14" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
     </row>
     <row r="20" spans="1:13" ht="18.75">
       <c r="A20" s="5" t="s">
@@ -2804,85 +2753,59 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="D23" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>182</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A24" s="7"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A25" s="7"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A26" s="7"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A27" s="7"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A28" s="7"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A29" s="7"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A30" s="7"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A31" s="7"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A32" s="7"/>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A33" s="7"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A34" s="7"/>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A35" s="7"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A36" s="7"/>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="7"/>
@@ -2939,73 +2862,47 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>182</v>
+        <v>153</v>
+      </c>
+      <c r="B44" s="14">
+        <v>200</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="D44" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="F44" t="s">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G47" s="22" t="s">
-        <v>182</v>
-      </c>
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="G47" s="22"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="8">
@@ -3050,7 +2947,7 @@
   <dimension ref="A1:M234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" bestFit="true" customWidth="true" width="36.0" collapsed="false"/>
+    <col min="1" max="2" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21">
@@ -3088,7 +2985,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="12" t="s">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>89</v>
@@ -3096,7 +2993,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="12" t="s">
-        <v>182</v>
+        <v>84</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>89</v>
@@ -3104,7 +3001,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="12" t="s">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>89</v>
@@ -3112,7 +3009,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="23" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>54</v>
@@ -3120,7 +3017,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="23" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>89</v>
@@ -3128,7 +3025,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="23" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>54</v>
@@ -3136,7 +3033,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="23" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>54</v>
@@ -3144,7 +3041,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="23" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>89</v>
@@ -3175,7 +3072,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="12" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>54</v>
@@ -3183,7 +3080,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="23" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>54</v>
@@ -3191,7 +3088,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="23" t="s">
-        <v>182</v>
+        <v>92</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>54</v>
@@ -3199,7 +3096,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="23" t="s">
-        <v>182</v>
+        <v>93</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>54</v>
@@ -3207,7 +3104,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="23" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>54</v>
@@ -3215,7 +3112,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="23" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>54</v>
@@ -3223,7 +3120,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="23" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>54</v>
@@ -3231,7 +3128,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="24" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>54</v>
@@ -3255,7 +3152,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="12" t="s">
-        <v>182</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3500,7 +3397,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="12" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="B68" s="24" t="s">
         <v>89</v>
@@ -3528,7 +3425,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="12" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="B73" s="24" t="s">
         <v>89</v>
@@ -3536,7 +3433,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="25" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="B74" s="24" t="s">
         <v>89</v>
@@ -3560,7 +3457,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="12" t="s">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="B78" s="24" t="s">
         <v>54</v>
@@ -3568,7 +3465,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="25" t="s">
-        <v>182</v>
+        <v>88</v>
       </c>
       <c r="B79" s="24" t="s">
         <v>89</v>
@@ -3576,7 +3473,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="25" t="s">
-        <v>182</v>
+        <v>121</v>
       </c>
       <c r="B80" s="24" t="s">
         <v>89</v>
@@ -3584,7 +3481,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="25" t="s">
-        <v>182</v>
+        <v>104</v>
       </c>
       <c r="B81" s="24" t="s">
         <v>54</v>
@@ -3592,7 +3489,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="25" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="B82" s="24" t="s">
         <v>54</v>
@@ -3600,7 +3497,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="25" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="B83" s="24" t="s">
         <v>148</v>
@@ -3608,7 +3505,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="25" t="s">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="B84" s="24" t="s">
         <v>148</v>
@@ -3616,7 +3513,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="25" t="s">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="B85" s="24" t="s">
         <v>54</v>
@@ -3624,7 +3521,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="B86" s="24" t="s">
         <v>54</v>
@@ -3632,7 +3529,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="25" t="s">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="B87" s="24" t="s">
         <v>89</v>
@@ -3656,7 +3553,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="12" t="s">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="B91" s="24" t="s">
         <v>54</v>
@@ -3664,7 +3561,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="25" t="s">
-        <v>182</v>
+        <v>103</v>
       </c>
       <c r="B92" s="24" t="s">
         <v>54</v>
@@ -3688,7 +3585,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="12" t="s">
-        <v>182</v>
+        <v>127</v>
       </c>
       <c r="B96" s="24" t="s">
         <v>54</v>
@@ -3696,7 +3593,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="25" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="B97" s="24" t="s">
         <v>54</v>
@@ -3720,7 +3617,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="12" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="B101" s="24" t="s">
         <v>54</v>
@@ -3728,7 +3625,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="25" t="s">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="B102" s="24" t="s">
         <v>54</v>
@@ -3736,7 +3633,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="25" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="B103" s="24" t="s">
         <v>54</v>
@@ -3744,7 +3641,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="25" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="B104" s="24" t="s">
         <v>54</v>
@@ -3752,7 +3649,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="25" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="B105" s="24" t="s">
         <v>54</v>
@@ -3760,7 +3657,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="25" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="B106" s="24" t="s">
         <v>54</v>
@@ -3768,7 +3665,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="25" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="B107" s="24" t="s">
         <v>54</v>
@@ -3776,7 +3673,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="25" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="B108" s="24" t="s">
         <v>54</v>
@@ -3784,7 +3681,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="25" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="B109" s="24" t="s">
         <v>54</v>
@@ -3792,7 +3689,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="25" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="B110" s="24" t="s">
         <v>54</v>
@@ -3800,7 +3697,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="25" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="B111" s="24" t="s">
         <v>54</v>
@@ -3824,7 +3721,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="12" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="B115" s="24" t="s">
         <v>148</v>
@@ -3832,7 +3729,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="25" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="B116" s="24" t="s">
         <v>148</v>
@@ -3840,7 +3737,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="25" t="s">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="B117" s="24" t="s">
         <v>148</v>
@@ -3848,7 +3745,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="25" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="B118" s="24" t="s">
         <v>148</v>
@@ -3856,7 +3753,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="25" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="B119" s="24" t="s">
         <v>54</v>
@@ -3864,7 +3761,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="25" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="B120" s="24" t="s">
         <v>54</v>
@@ -3872,7 +3769,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="25" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B121" s="24" t="s">
         <v>89</v>
@@ -3896,7 +3793,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="12" t="s">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="B125" s="24" t="s">
         <v>54</v>
@@ -3904,7 +3801,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="25" t="s">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="B126" s="24" t="s">
         <v>54</v>
@@ -3912,7 +3809,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="25" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="B127" s="24" t="s">
         <v>148</v>
@@ -3920,7 +3817,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="25" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="B128" s="24" t="s">
         <v>54</v>
@@ -3928,7 +3825,7 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="25" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
       <c r="B129" s="24" t="s">
         <v>54</v>
@@ -3936,7 +3833,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="25" t="s">
-        <v>182</v>
+        <v>117</v>
       </c>
       <c r="B130" s="24" t="s">
         <v>54</v>
@@ -3944,7 +3841,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="25" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="B131" s="24" t="s">
         <v>89</v>
@@ -3952,7 +3849,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="25" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="B132" s="24" t="s">
         <v>148</v>
@@ -3960,7 +3857,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="25" t="s">
-        <v>182</v>
+        <v>112</v>
       </c>
       <c r="B133" s="24" t="s">
         <v>148</v>
@@ -3968,7 +3865,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="25" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B134" s="24" t="s">
         <v>148</v>
@@ -3976,7 +3873,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="25" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B135" s="24" t="s">
         <v>148</v>
@@ -3984,7 +3881,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="25" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B136" s="24" t="s">
         <v>148</v>
@@ -3992,7 +3889,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="25" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B137" s="24" t="s">
         <v>148</v>
@@ -4038,14 +3935,14 @@
   <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="18.42578125" collapsed="false"/>
-    <col min="2" max="2" customWidth="true" width="18.28515625" collapsed="false"/>
-    <col min="3" max="3" customWidth="true" width="18.140625" collapsed="false"/>
-    <col min="4" max="4" customWidth="true" width="18.28515625" collapsed="false"/>
-    <col min="5" max="6" customWidth="true" width="18.42578125" collapsed="false"/>
-    <col min="7" max="7" customWidth="true" width="18.140625" collapsed="false"/>
-    <col min="8" max="11" customWidth="true" width="18.42578125" collapsed="false"/>
-    <col min="12" max="13" customWidth="true" width="18.28515625" collapsed="false"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="6" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22.5" customHeight="1">
